--- a/data/gravel/Ridley Kanzo Adventure 2025.xlsx
+++ b/data/gravel/Ridley Kanzo Adventure 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C63022E-F572-8742-9681-0DDDEEB17664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8670FEFE-ECD3-FA4A-B106-AA92CD262384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2680" yWindow="860" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34560" yWindow="-18600" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="100">
   <si>
     <t>brand</t>
   </si>
@@ -314,6 +314,12 @@
   </si>
   <si>
     <t>https://www.ridley-bikes.com/en_US/bikes/SBIKADRID298</t>
+  </si>
+  <si>
+    <t>press fit</t>
+  </si>
+  <si>
+    <t>no</t>
   </si>
 </sst>
 </file>
@@ -1354,6 +1360,21 @@
       <c r="A26" t="s">
         <v>42</v>
       </c>
+      <c r="C26">
+        <v>1260</v>
+      </c>
+      <c r="D26">
+        <v>1290</v>
+      </c>
+      <c r="E26">
+        <v>1310</v>
+      </c>
+      <c r="F26">
+        <v>1360</v>
+      </c>
+      <c r="G26">
+        <v>1390</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
@@ -1515,7 +1536,7 @@
         <v>52</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -1575,6 +1596,9 @@
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>62</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/gravel/Ridley Kanzo Adventure 2025.xlsx
+++ b/data/gravel/Ridley Kanzo Adventure 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8670FEFE-ECD3-FA4A-B106-AA92CD262384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA7D44B-DEC7-194C-B187-947265206219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34560" yWindow="-18600" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/gravel/Ridley Kanzo Adventure 2025.xlsx
+++ b/data/gravel/Ridley Kanzo Adventure 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA7D44B-DEC7-194C-B187-947265206219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59DEE77-4B8D-134A-B00A-39C304E48077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8260" yWindow="700" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="101">
   <si>
     <t>brand</t>
   </si>
@@ -320,6 +320,9 @@
   </si>
   <si>
     <t>no</t>
+  </si>
+  <si>
+    <t>https://images.cyclingfactory.be/transform/eyJidWNrZXQiOiJiY2YtYjJiLWltYWdlcyIsImtleSI6IktBTlpPQURWRU5UVVJFN0U3X2ltYWdlXzAzMjIwNjM0YmNmYWQwNzBmYzlhMjQ1NDdhNDY0ZjcyNTEwMjAzMzNfMzg0MHgucG5nIiwiZWRpdHMiOnsicmVzaXplIjp7IndpZHRoIjoxMDI0LCJ3aXRob3V0RW5sYXJnZW1lbnQiOnRydWV9LCJ3ZWJwIjp7InF1YWxpdHkiOjYwfX19</t>
   </si>
 </sst>
 </file>
@@ -705,6 +708,11 @@
         <v>97</v>
       </c>
     </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>100</v>
+      </c>
+    </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>

--- a/data/gravel/Ridley Kanzo Adventure 2025.xlsx
+++ b/data/gravel/Ridley Kanzo Adventure 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59DEE77-4B8D-134A-B00A-39C304E48077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24059262-11AF-C646-B296-88B5C8F541B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8260" yWindow="700" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="103">
   <si>
     <t>brand</t>
   </si>
@@ -310,9 +310,6 @@
     <t>size</t>
   </si>
   <si>
-    <t>euros</t>
-  </si>
-  <si>
     <t>https://www.ridley-bikes.com/en_US/bikes/SBIKADRID298</t>
   </si>
   <si>
@@ -323,6 +320,15 @@
   </si>
   <si>
     <t>https://images.cyclingfactory.be/transform/eyJidWNrZXQiOiJiY2YtYjJiLWltYWdlcyIsImtleSI6IktBTlpPQURWRU5UVVJFN0U3X2ltYWdlXzAzMjIwNjM0YmNmYWQwNzBmYzlhMjQ1NDdhNDY0ZjcyNTEwMjAzMzNfMzg0MHgucG5nIiwiZWRpdHMiOnsicmVzaXplIjp7IndpZHRoIjoxMDI0LCJ3aXRob3V0RW5sYXJnZW1lbnQiOnRydWV9LCJ3ZWJwIjp7InF1YWxpdHkiOjYwfX19</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Beringen, Flanders, Belgium</t>
+  </si>
+  <si>
+    <t>EUR</t>
   </si>
 </sst>
 </file>
@@ -662,7 +668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N71"/>
+  <dimension ref="A1:N72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -705,12 +711,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1544,7 +1550,7 @@
         <v>52</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -1606,7 +1612,7 @@
         <v>62</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -1742,7 +1748,15 @@
         <v>85</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>100</v>
+      </c>
+      <c r="B72" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Ridley Kanzo Adventure 2025.xlsx
+++ b/data/gravel/Ridley Kanzo Adventure 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24059262-11AF-C646-B296-88B5C8F541B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82874F43-99F4-6A4B-B77F-EAE8226DF1F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -329,6 +329,24 @@
   </si>
   <si>
     <t>EUR</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -668,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N72"/>
+  <dimension ref="A1:N78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1609,153 +1627,183 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>62</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>64</v>
-      </c>
-      <c r="B50">
-        <v>27.2</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>68</v>
+        <v>62</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="B56">
+        <v>27.2</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>73</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>78</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>81</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>82</v>
-      </c>
-      <c r="B68" s="1">
-        <v>2499</v>
+        <v>76</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>84</v>
+        <v>78</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" s="1">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>85</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>100</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B78" t="s">
         <v>101</v>
       </c>
     </row>
